--- a/workshop/3e2917d26b.xlsx
+++ b/workshop/3e2917d26b.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="素材清单（人工去挑）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -2401,161 +2401,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>场景</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>检索词（英文，主用）</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>建议条数</t>
-        </is>
-      </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+          <t>覆盖镜次</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>怎么做（检索词 / 拍摄内容）</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>去哪找</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>要几条</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>片头钩子 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>001-002</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>自己拍（手机横屏）</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>厂房外景</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>005、009、013、017、021、025、029、033</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>车间内景</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>006、010、014、018、022、026、030、034</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>empty factory / idle production line</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>003、007、011、015、019、023、027、031</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>empty warehouse / cleared shelves</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>货车物流</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>004、008、012、016、020、024、028、032</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>empty loading dock / idle truck</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>L1 自制</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>数据图表 · Excel 出图（叠加层）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>011-012、034</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>车间内景</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>empty factory / idle production line</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>片尾落点 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>035-036</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>自己拍</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>货车物流</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Pexels/Pixabay 免署名可商用（注意顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账。</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>L3 AI 兜底</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>仅在实拍和素材站都拿不到时启用</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workshop/3e2917d26b.xlsx
+++ b/workshop/3e2917d26b.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：81.0 秒　镜次：36</t>
+          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：74.2 秒　镜次：32</t>
         </is>
       </c>
     </row>
@@ -595,14 +595,14 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>说关就关</t>
+          <t>不是行情差</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -644,17 +644,17 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>钱到底卡在哪</t>
+          <t>是现金先断了</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>1.9</v>
@@ -744,17 +744,17 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>症结在订单依赖</t>
+          <t>栽在「倒闭 / 关停」上</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -792,27 +792,27 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>账期拉长，成本上升三头一起压</t>
+          <t>先把事实摆出来</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>推进</t>
+          <t>陈述/数字重音</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>空镜</t>
+          <t>图表+实拍</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -824,12 +824,12 @@
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>开场悬念</t>
+          <t>中段推进</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>叠化</t>
+          <t>硬切</t>
         </is>
       </c>
     </row>
@@ -840,17 +840,17 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>先把事实说清楚</t>
+          <t>无锡迁镇江的精细化工企业格林艾普</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -888,17 +888,17 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>无锡迁镇江的精细化工企业格林艾普</t>
+          <t>因产业结构老化</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -936,17 +936,17 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>1.6</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>因产业结构老化</t>
+          <t>产品与市场脱节</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -984,17 +984,17 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>产品与市场脱节</t>
+          <t>叠加搬迁“塌方式腐败”致预算超标</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1032,17 +1032,17 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>19.5</v>
+        <v>21.1</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>叠加搬迁“塌方式腐败”致预算超标</t>
+          <t>资金链断裂，2014年申请破产</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1060,8 +1060,16 @@
           <t>【待挑】倒闭关停_车间内景_010　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：2014年</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1080,27 +1088,27 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>19.5</v>
+        <v>21.1</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>资金链断裂，2014年申请破产</t>
+          <t>打个比方</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>陈述/数字重音</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>图表+实拍</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1108,16 +1116,8 @@
           <t>【待挑】倒闭关停_仓库_011　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：2014年</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1136,27 +1136,27 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2015年宣告破产</t>
+          <t>厂子就是一口锅</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>陈述/数字重音</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>图表+实拍</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1164,16 +1164,8 @@
           <t>【待挑】倒闭关停_货车物流_012　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：2015年</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1192,17 +1184,17 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>26.3</v>
+        <v>27.2</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>打个比方</t>
+          <t>订单是火，现金是锅里的水</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1240,17 +1232,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>26.3</v>
+        <v>27.2</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>28.1</v>
+        <v>29.1</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>厂子就是一口锅</t>
+          <t>火一停，水凉得飞快</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1288,27 +1280,27 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>28.1</v>
+        <v>29.1</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>订单是火，现金是锅里的水</t>
+          <t>本案的财务病灶很具体</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>逐条拆解</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>图表+文字卡</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1336,27 +1328,27 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>32.5</v>
+        <v>33.1</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>1.9</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>火一停，水凉得飞快</t>
+          <t>搬迁项目塌方式腐败</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>逐条拆解</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>图表+文字卡</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1384,17 +1376,17 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>32.5</v>
+        <v>33.1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>①战略视角</t>
+          <t>资本开支成无底洞</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1412,11 +1404,7 @@
           <t>【待挑】倒闭关停_厂房外景_017　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：战略视角</t>
-        </is>
-      </c>
+      <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1436,17 +1424,17 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>36.1</v>
+        <v>37.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>是否死守低端红海</t>
+          <t>工程超支直接吃掉安全垫</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1484,17 +1472,17 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>36.1</v>
+        <v>37.2</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>38.8</v>
+        <v>39.9</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>2.7</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>无产品壁垒，靠低价内卷抢单</t>
+          <t>把这家化工材料厂的账拆开看</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1532,17 +1520,17 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>38.8</v>
+        <v>39.9</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>40.6</v>
+        <v>43.3</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>②财务视角</t>
+          <t>倒闭极少突发，是现金循环周期被拉长</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1560,11 +1548,7 @@
           <t>【待挑】倒闭关停_货车物流_020　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：财务视角</t>
-        </is>
-      </c>
+      <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -1584,17 +1568,17 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>40.6</v>
+        <v>43.3</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>42.4</v>
+        <v>45.4</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>现金流是否断裂</t>
+          <t>应收收不回，存货压钱</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1632,17 +1616,17 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>42.4</v>
+        <v>45.4</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>45.7</v>
+        <v>48.1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>应收账款/账期是否被大客户拉长抽</t>
+          <t>扩产吞现金，三条管道同时漏</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1680,17 +1664,17 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>45.7</v>
+        <v>48.1</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>47.5</v>
+        <v>50.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>③运营视角</t>
+          <t>安全垫撑不到回款那天</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1708,11 +1692,7 @@
           <t>【待挑】倒闭关停_仓库_023　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：运营视角</t>
-        </is>
-      </c>
+      <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr">
         <is>
@@ -1732,17 +1712,17 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>47.5</v>
+        <v>50.2</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>50.9</v>
+        <v>52.1</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>成本结构是否失衡（原料涨，终端不涨，增收不增利）</t>
+          <t>看三数，安全垫月数</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1780,17 +1760,17 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>50.9</v>
+        <v>52.1</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>52.7</v>
+        <v>54.6</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>④心智视角</t>
+          <t>应收周转天数，资产负债率</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1808,11 +1788,7 @@
           <t>【待挑】倒闭关停_厂房外景_025　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：心智视角</t>
-        </is>
-      </c>
+      <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -1832,27 +1808,27 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>52.7</v>
+        <v>54.6</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>54.5</v>
+        <v>56.7</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>老板是否路径依赖</t>
+          <t>关门不是哪一天的决定</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1880,27 +1856,27 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>54.5</v>
+        <v>56.7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>57.6</v>
+        <v>59.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>不愿技改升级，把困境归咎大环境</t>
+          <t>是每一次「再撑撑」的累加</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1928,27 +1904,27 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>57.6</v>
+        <v>59.2</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>59.5</v>
+        <v>62.7</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>公开信息点名的问题</t>
+          <t>记住一句话，潮水退了才知道谁没穿裤</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1956,16 +1932,24 @@
           <t>【待挑】倒闭关停_货车物流_028　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -1976,27 +1960,27 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>59.5</v>
+        <v>62.7</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>62.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>产业结构老化，产品与市场脱节</t>
+          <t>安全垫比规模重要</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2004,16 +1988,24 @@
           <t>【待挑】倒闭关停_厂房外景_029　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -2024,27 +2016,27 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>62.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>65.8</v>
+        <v>69.3</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>搬迁项目塌方式腐败致工程预算严重超标</t>
+          <t>同类厂记住三件事，①留足 6 个月现金安全垫再扩张</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2052,16 +2044,24 @@
           <t>【待挑】倒闭关停_车间内景_030　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：6 个月</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -2072,27 +2072,27 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>65.8</v>
+        <v>69.3</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>67.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>关门不是哪一天的决定</t>
+          <t>②砍掉不赚钱的低端红海单</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2100,16 +2100,24 @@
           <t>【待挑】倒闭关停_仓库_031　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -2120,27 +2128,27 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>67.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>70.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>是每一次「再撑撑」的累加</t>
+          <t>③每年固定比例投技改</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2148,238 +2156,22 @@
           <t>【待挑】倒闭关停_货车物流_032　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>硬切</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>033</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>最后给同类厂三句话</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_厂房外景_033　搜：abandoned warehouse / factory closed / shutter door</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>避坑清单上屏（≤3 条）</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>结论咚</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>034</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>①留足 6 个月现金安全垫再扩张</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_车间内景_034　搜：empty factory / idle production line</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：6 个月</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>035</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>②砍掉不赚钱的低端红海单</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_仓库_035　搜：empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>避坑清单上屏（≤3 条）</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>结论咚</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>036</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>③每年固定比例投技改</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_货车物流_036　搜：empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>避坑清单上屏（≤3 条）</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>结论咚</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>叠化</t>
         </is>
@@ -2524,7 +2316,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>005、009、013、017、021、025、029、033</t>
+          <t>005、009、013、017、021、025、029</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -2544,7 +2336,7 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2359,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>006、010、014、018、022、026、030、034</t>
+          <t>006、010、014、018、022、026、030</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -2587,7 +2379,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2402,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>003、007、011、015、019、023、027、031</t>
+          <t>003、007、011、015、019、023、027</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -2630,7 +2422,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2445,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>004、008、012、016、020、024、028、032</t>
+          <t>004、008、012、016、020、024、028</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -2673,7 +2465,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2488,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>011-012、034</t>
+          <t>010、030</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2739,7 +2531,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>035-036</t>
+          <t>031-032</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">

--- a/workshop/3e2917d26b.xlsx
+++ b/workshop/3e2917d26b.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：74.2 秒　镜次：32</t>
+          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：73.9 秒　镜次：31</t>
         </is>
       </c>
     </row>
@@ -747,14 +747,14 @@
         <v>4.1</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>栽在「倒闭 / 关停」上</t>
+          <t>就这么倒下了</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>1.6</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>11.5</v>
+        <v>10.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>3.3</v>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>11.5</v>
+        <v>10.2</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>13.1</v>
+        <v>11.8</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1.6</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>13.1</v>
+        <v>11.8</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>1.6</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3.3</v>
@@ -1032,17 +1032,17 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>21.1</v>
+        <v>18.3</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>资金链断裂，2014年申请破产</t>
+          <t>资金链断裂</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1060,16 +1060,8 @@
           <t>【待挑】倒闭关停_车间内景_010　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：2014年</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I14" s="8" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1088,10 +1080,10 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>21.1</v>
+        <v>18.3</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>1.8</v>
@@ -1136,17 +1128,17 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>24.7</v>
+        <v>22.6</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>厂子就是一口锅</t>
+          <t>做生意像种地，现金是雨水</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1184,17 +1176,17 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>24.7</v>
+        <v>22.6</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>订单是火，现金是锅里的水</t>
+          <t>连旱三年，再肥的地也长不出庄稼</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1232,27 +1224,27 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>29.1</v>
+        <v>27.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1.9</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>火一停，水凉得飞快</t>
+          <t>问题出在哪，一句话</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>逐条拆解</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>图表+文字卡</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1280,17 +1272,17 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>29.1</v>
+        <v>27.6</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>31.2</v>
+        <v>29.9</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>本案的财务病灶很具体</t>
+          <t>搬迁成了某些人的提款机</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1328,17 +1320,17 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>31.2</v>
+        <v>29.9</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>33.1</v>
+        <v>31.7</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>搬迁项目塌方式腐败</t>
+          <t>工程预算一路超支</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1376,17 +1368,17 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>33.1</v>
+        <v>31.7</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>34.9</v>
+        <v>33.6</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>资本开支成无底洞</t>
+          <t>安全垫被一点点啃光</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1424,17 +1416,17 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>34.9</v>
+        <v>33.6</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>37.2</v>
+        <v>36.3</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>工程超支直接吃掉安全垫</t>
+          <t>把这家化工材料厂的账说人话</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1472,17 +1464,17 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>37.2</v>
+        <v>36.3</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>39.9</v>
+        <v>39.2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>把这家化工材料厂的账拆开看</t>
+          <t>倒闭很少突然，都是钱慢慢流干</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1520,17 +1512,17 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>39.9</v>
+        <v>39.2</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>倒闭极少突发，是现金循环周期被拉长</t>
+          <t>客户拖着货款不给</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1568,17 +1560,17 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>45.4</v>
+        <v>44.1</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>应收收不回，存货压钱</t>
+          <t>仓库货卖不掉，老板还借钱上新线</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1616,17 +1608,17 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>45.4</v>
+        <v>44.1</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>扩产吞现金，三条管道同时漏</t>
+          <t>三条水管一起漏，家底撑不到回款那天就见了底</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1664,17 +1656,17 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>安全垫撑不到回款那天</t>
+          <t>你只盯三个数，兜里钱够花几个月</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1712,17 +1704,17 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>52.1</v>
+        <v>53.9</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>看三数，安全垫月数</t>
+          <t>客户拖你多少天，欠的钱是家底几倍</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1760,27 +1752,27 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>52.1</v>
+        <v>53.9</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>54.6</v>
+        <v>57</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>应收周转天数，资产负债率</t>
+          <t>撑不下去的厂，多半不是输给对手</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1808,17 +1800,17 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>54.6</v>
+        <v>57</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>56.7</v>
+        <v>58.8</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>关门不是哪一天的决定</t>
+          <t>是输给自己先干涸</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1856,27 +1848,27 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>56.7</v>
+        <v>58.8</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>59.2</v>
+        <v>62.3</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>是每一次「再撑撑」的累加</t>
+          <t>记住一句话，潮水退了才知道谁没穿裤</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1884,16 +1876,24 @@
           <t>【待挑】倒闭关停_仓库_027　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -1904,17 +1904,17 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>59.2</v>
+        <v>62.3</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>62.7</v>
+        <v>64.7</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>记住一句话，潮水退了才知道谁没穿裤</t>
+          <t>安全垫比规模重要</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1960,17 +1960,17 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>62.7</v>
+        <v>64.7</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>65.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>安全垫比规模重要</t>
+          <t>同类厂记住三件事，①兜里先留够半年的活钱再扩张</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2016,17 +2016,17 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>65.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>69.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>同类厂记住三件事，①留足 6 个月现金安全垫再扩张</t>
+          <t>②不赚钱的低价单该砍就砍</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>数字上大字幕：6 个月</t>
+          <t>避坑清单上屏（≤3 条）</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>数字叮</t>
+          <t>结论咚</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -2072,17 +2072,17 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>69.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>71.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>②砍掉不赚钱的低端红海单</t>
+          <t>③每年匀一笔钱搞技术升级</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2116,62 +2116,6 @@
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>032</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>③每年固定比例投技改</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_货车物流_032　搜：empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>避坑清单上屏（≤3 条）</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>结论咚</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>叠化</t>
         </is>
@@ -2193,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2359,7 +2303,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>006、010、014、018、022、026、030</t>
+          <t>006、010、014、018、022、026</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -2379,7 +2323,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 6 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2478,27 +2422,27 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>L1 自制</t>
+          <t>L1 自拍</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>数据图表 · Excel 出图（叠加层）</t>
+          <t>片尾落点 · 自拍空镜</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>010、030</t>
+          <t>030-031</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
+          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
+          <t>自己拍</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -2508,94 +2452,51 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
+          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>L1 自拍</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>片尾落点 · 自拍空镜</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>031-032</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>自己拍</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>L3 AI 兜底</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>仅在实拍和素材站都拿不到时启用</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>按需</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
         </is>
@@ -2603,7 +2504,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A10:I10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
